--- a/vse-loti/340203791/spec-340203791.xlsx
+++ b/vse-loti/340203791/spec-340203791.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -35,11 +36,11 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,14 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,34 +525,533 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>57×3.5</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>604</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>191448.2</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>68608.23</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>83702.03</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>76×3.5</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>133954.1</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>66870.61</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>81582.14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>89×4</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>192098.36</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>65495.23</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>79904.17999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>108×4</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>560</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>5.746</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>381763.93</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>66444.44</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>81062.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>133×4.5</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>112179.34</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>63441.09</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>77398.13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>159×4.5</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>202480.66</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>68641.98</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>83743.22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>219×6</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>6.178</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>408290.49</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>66088.52</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>80627.99000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>273×6</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3.793</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>240157.38</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>63316.63</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>77246.28999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-57х3,5 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>57×3.5</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="5" t="n">
+        <v>17049.18</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-76х3,5 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>76×3.5</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="5" t="n">
+        <v>29098.36</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-89х4 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>89×4</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>47409.84</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-108х4,0 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>108×4</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" s="5" t="n">
+        <v>87909.84</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-133х4,5 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>133×4.5</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="5" t="n">
+        <v>14975.41</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-159х4,5 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>159×4.5</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" s="5" t="n">
+        <v>23422.13</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 90°-219х6 ГОСТ 17375-2001</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>219×6</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" s="5" t="n">
+        <v>40983.61</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F17" s="7" t="n">
+        <v>28.161</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>2123220.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G18" s="8" t="n">
+        <v>2123220.82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>2590329.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Источник: Извещение.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Расчет НМЦ.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="A20:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
